--- a/OPEC_Human_Verification v2.xlsx
+++ b/OPEC_Human_Verification v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/datle/Desktop/1 Research/From_Words_to_Barrels_Measuring_the_Incremental_Information_Content_of_OPEC_Narratives_for_Oil_Price/outputs/019fc64f-human-validation-combined/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AD3409-23F4-904C-B91C-94C54660B216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD609C7-4FB3-4348-8D7D-A6ED4369B515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Huong dan" sheetId="1" r:id="rId1"/>
@@ -5976,9 +5976,6 @@
     <t>participating in the Declaration of Cooperation, with the exception of Mexico, and as a result, the agreement is conditional on the consent of Mexico.</t>
   </si>
   <si>
-    <t>anhdat le</t>
-  </si>
-  <si>
     <t>File không chứa nhãn mô hình hay bảng ánh xạ riêng. Ngày tháng/tên sự kiện vẫn có thể xuất hiện trong văn bản nguồn: không coi đây là làm mù hoàn toàn danh tính sự kiện.</t>
   </si>
   <si>
@@ -6349,6 +6346,9 @@
   </si>
   <si>
     <t>Có bằng chứng maintain current oil production levels unchanged; thay đổi ròng mới = 0.</t>
+  </si>
+  <si>
+    <t>v2</t>
   </si>
 </sst>
 </file>
@@ -6733,7 +6733,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1308</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="76" customHeight="1">
@@ -6773,7 +6773,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="76" customHeight="1">
@@ -6956,23 +6956,23 @@
         <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3">
         <v>4</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>1328</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>1329</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1">
@@ -6983,17 +6983,17 @@
         <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1">
@@ -7004,23 +7004,23 @@
         <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <v>3</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1">
@@ -7031,17 +7031,17 @@
         <v>57</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1">
@@ -7052,10 +7052,10 @@
         <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E6" s="4">
         <v>-1.5</v>
@@ -7064,13 +7064,13 @@
         <v>4</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1">
@@ -7081,17 +7081,17 @@
         <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1">
@@ -7102,10 +7102,10 @@
         <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -7114,13 +7114,13 @@
         <v>4</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1">
@@ -7131,23 +7131,23 @@
         <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <v>4</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="60" customHeight="1">
@@ -7158,23 +7158,23 @@
         <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3">
         <v>4</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="60" customHeight="1">
@@ -7185,23 +7185,23 @@
         <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3">
         <v>4</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="60" customHeight="1">
@@ -7212,17 +7212,17 @@
         <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1">
@@ -7233,17 +7233,17 @@
         <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60" customHeight="1">
@@ -7254,23 +7254,23 @@
         <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="3">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="60" customHeight="1">
@@ -7281,23 +7281,23 @@
         <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="3">
         <v>3</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="60" customHeight="1">
@@ -7308,17 +7308,17 @@
         <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" customHeight="1">
@@ -7329,17 +7329,17 @@
         <v>81</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" customHeight="1">
@@ -7350,17 +7350,17 @@
         <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" customHeight="1">
@@ -7371,23 +7371,23 @@
         <v>85</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="3">
         <v>4</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" customHeight="1">
@@ -7398,23 +7398,23 @@
         <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="3">
         <v>4</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" customHeight="1">
@@ -7425,17 +7425,17 @@
         <v>89</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" customHeight="1">
@@ -7446,23 +7446,23 @@
         <v>91</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="3">
         <v>4</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" customHeight="1">
@@ -7473,17 +7473,17 @@
         <v>93</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" customHeight="1">
@@ -7494,17 +7494,17 @@
         <v>95</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" customHeight="1">
@@ -7515,17 +7515,17 @@
         <v>97</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" customHeight="1">
@@ -7536,10 +7536,10 @@
         <v>99</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E26" s="4">
         <v>0.54800000000000004</v>
@@ -7548,13 +7548,13 @@
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>1371</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" customHeight="1">
@@ -7565,23 +7565,23 @@
         <v>101</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="3">
         <v>4</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" customHeight="1">
@@ -7592,17 +7592,17 @@
         <v>103</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" customHeight="1">
@@ -7613,23 +7613,23 @@
         <v>105</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="3">
         <v>4</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" customHeight="1">
@@ -7640,10 +7640,10 @@
         <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E30" s="4">
         <v>0.5</v>
@@ -7652,13 +7652,13 @@
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>1374</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>1375</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" customHeight="1">
@@ -7669,10 +7669,10 @@
         <v>109</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E31" s="4">
         <v>0.41099999999999998</v>
@@ -7681,13 +7681,13 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" customHeight="1">
@@ -7698,23 +7698,23 @@
         <v>111</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="3">
         <v>4</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="60" customHeight="1">
@@ -7725,23 +7725,23 @@
         <v>113</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="3">
         <v>4</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="60" customHeight="1">
@@ -7752,17 +7752,17 @@
         <v>115</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="60" customHeight="1">
@@ -7773,17 +7773,17 @@
         <v>117</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="60" customHeight="1">
@@ -7794,10 +7794,10 @@
         <v>119</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E36" s="4">
         <v>0.41099999999999998</v>
@@ -7806,13 +7806,13 @@
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="60" customHeight="1">
@@ -7823,23 +7823,23 @@
         <v>121</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="3">
         <v>4</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="60" customHeight="1">
@@ -7850,17 +7850,17 @@
         <v>123</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="60" customHeight="1">
@@ -7871,10 +7871,10 @@
         <v>125</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E39" s="4">
         <v>0.20599999999999999</v>
@@ -7883,13 +7883,13 @@
         <v>3</v>
       </c>
       <c r="G39" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>1415</v>
-      </c>
       <c r="I39" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="60" customHeight="1">
@@ -7900,23 +7900,23 @@
         <v>127</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="3">
         <v>4</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="60" customHeight="1">
@@ -7927,23 +7927,23 @@
         <v>129</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="3">
         <v>4</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="60" customHeight="1">
@@ -7954,23 +7954,23 @@
         <v>131</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="3">
         <v>4</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="60" customHeight="1">
@@ -7981,10 +7981,10 @@
         <v>133</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E43" s="4">
         <v>-2.2000000000000002</v>
@@ -7993,13 +7993,13 @@
         <v>3</v>
       </c>
       <c r="G43" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>1416</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>1417</v>
-      </c>
       <c r="I43" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="60" customHeight="1">
@@ -8010,17 +8010,17 @@
         <v>135</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="60" customHeight="1">
@@ -8031,10 +8031,10 @@
         <v>137</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E45" s="4">
         <v>0.5</v>
@@ -8043,13 +8043,13 @@
         <v>4</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="60" customHeight="1">
@@ -8060,17 +8060,17 @@
         <v>139</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="4"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="60" customHeight="1">
@@ -8081,23 +8081,23 @@
         <v>141</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="3">
         <v>4</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="60" customHeight="1">
@@ -8108,10 +8108,10 @@
         <v>143</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E48" s="4">
         <v>-2</v>
@@ -8120,13 +8120,13 @@
         <v>4</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="60" customHeight="1">
@@ -8137,23 +8137,23 @@
         <v>145</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="3">
         <v>4</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="60" customHeight="1">
@@ -8164,23 +8164,23 @@
         <v>147</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="3">
         <v>4</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="60" customHeight="1">
@@ -8191,17 +8191,17 @@
         <v>149</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="4"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="60" customHeight="1">
@@ -8212,17 +8212,17 @@
         <v>151</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="60" customHeight="1">
@@ -8233,17 +8233,17 @@
         <v>153</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="4"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="60" customHeight="1">
@@ -8254,17 +8254,17 @@
         <v>155</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="60" customHeight="1">
@@ -8275,17 +8275,17 @@
         <v>157</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="60" customHeight="1">
@@ -8296,23 +8296,23 @@
         <v>159</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="3">
         <v>4</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="60" customHeight="1">
@@ -8323,23 +8323,23 @@
         <v>161</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="3">
         <v>4</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="60" customHeight="1">
@@ -8350,23 +8350,23 @@
         <v>163</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="3">
         <v>4</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="60" customHeight="1">
@@ -8377,23 +8377,23 @@
         <v>165</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="3">
         <v>4</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="60" customHeight="1">
@@ -8404,10 +8404,10 @@
         <v>167</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E60" s="4">
         <v>0.5</v>
@@ -8416,13 +8416,13 @@
         <v>4</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="60" customHeight="1">
@@ -8433,23 +8433,23 @@
         <v>169</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="3">
         <v>3</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="60" customHeight="1">
@@ -8460,23 +8460,23 @@
         <v>171</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="3">
         <v>4</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="60" customHeight="1">
@@ -8487,17 +8487,17 @@
         <v>173</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="4"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="60" customHeight="1">
@@ -8508,10 +8508,10 @@
         <v>175</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E64" s="4">
         <v>-1</v>
@@ -8520,13 +8520,13 @@
         <v>4</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="60" customHeight="1">
@@ -8537,10 +8537,10 @@
         <v>177</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E65" s="4">
         <v>0.15</v>
@@ -8549,13 +8549,13 @@
         <v>4</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="60" customHeight="1">
@@ -8566,10 +8566,10 @@
         <v>179</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -8578,13 +8578,13 @@
         <v>4</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="60" customHeight="1">
@@ -8595,23 +8595,23 @@
         <v>181</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="3">
         <v>4</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="60" customHeight="1">
@@ -8622,17 +8622,17 @@
         <v>183</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="4"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="60" customHeight="1">
@@ -8643,23 +8643,23 @@
         <v>185</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="3">
         <v>4</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="60" customHeight="1">
@@ -8670,17 +8670,17 @@
         <v>187</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="4"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="60" customHeight="1">
@@ -8691,17 +8691,17 @@
         <v>189</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="60" customHeight="1">
@@ -8712,17 +8712,17 @@
         <v>191</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="4"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="60" customHeight="1">
@@ -8733,10 +8733,10 @@
         <v>193</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E73" s="4">
         <v>0.54700000000000004</v>
@@ -8745,13 +8745,13 @@
         <v>5</v>
       </c>
       <c r="G73" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>1394</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>1395</v>
-      </c>
       <c r="I73" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="60" customHeight="1">
@@ -8762,17 +8762,17 @@
         <v>195</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="4"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="60" customHeight="1">
@@ -8783,10 +8783,10 @@
         <v>197</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -8795,13 +8795,13 @@
         <v>4</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="60" customHeight="1">
@@ -8812,10 +8812,10 @@
         <v>199</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E76" s="4">
         <v>0.20599999999999999</v>
@@ -8824,13 +8824,13 @@
         <v>3</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="60" customHeight="1">
@@ -8841,17 +8841,17 @@
         <v>201</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="4"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="60" customHeight="1">
@@ -8862,23 +8862,23 @@
         <v>203</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="3">
         <v>4</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="60" customHeight="1">
@@ -8889,23 +8889,23 @@
         <v>205</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="3">
         <v>3</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="60" customHeight="1">
@@ -8916,23 +8916,23 @@
         <v>207</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="3">
         <v>4</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="60" customHeight="1">
@@ -8943,17 +8943,17 @@
         <v>209</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="4"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="60" customHeight="1">
@@ -8964,10 +8964,10 @@
         <v>211</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E82" s="4">
         <v>-4.2</v>
@@ -8976,13 +8976,13 @@
         <v>4</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="60" customHeight="1">
@@ -8993,10 +8993,10 @@
         <v>213</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E83" s="4">
         <v>0.41099999999999998</v>
@@ -9005,13 +9005,13 @@
         <v>5</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="60" customHeight="1">
@@ -9022,10 +9022,10 @@
         <v>215</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -9034,13 +9034,13 @@
         <v>4</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="60" customHeight="1">
@@ -9051,23 +9051,23 @@
         <v>217</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="3">
         <v>4</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="60" customHeight="1">
@@ -9078,10 +9078,10 @@
         <v>219</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E86" s="4">
         <v>-1.2</v>
@@ -9090,13 +9090,13 @@
         <v>4</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="60" customHeight="1">
@@ -9107,23 +9107,23 @@
         <v>221</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="3">
         <v>3</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="60" customHeight="1">
@@ -9134,17 +9134,17 @@
         <v>223</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="4"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="60" customHeight="1">
@@ -9155,17 +9155,17 @@
         <v>225</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="4"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="60" customHeight="1">
@@ -9176,10 +9176,10 @@
         <v>227</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E90" s="4">
         <v>0.188</v>
@@ -9188,13 +9188,13 @@
         <v>3</v>
       </c>
       <c r="G90" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>1426</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>1427</v>
-      </c>
       <c r="I90" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="60" customHeight="1">
@@ -9205,23 +9205,23 @@
         <v>229</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="3">
         <v>4</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="60" customHeight="1">
@@ -9232,23 +9232,23 @@
         <v>231</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="3">
         <v>4</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="60" customHeight="1">
@@ -9259,17 +9259,17 @@
         <v>233</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="4"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="60" customHeight="1">
@@ -9280,10 +9280,10 @@
         <v>235</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E94" s="4">
         <v>0.188</v>
@@ -9292,13 +9292,13 @@
         <v>3</v>
       </c>
       <c r="G94" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>1426</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>1427</v>
-      </c>
       <c r="I94" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="60" customHeight="1">
@@ -9309,17 +9309,17 @@
         <v>237</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="4"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="60" customHeight="1">
@@ -9330,17 +9330,17 @@
         <v>239</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="60" customHeight="1">
@@ -9351,23 +9351,23 @@
         <v>241</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="3">
         <v>4</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="60" customHeight="1">
@@ -9378,23 +9378,23 @@
         <v>243</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="3">
         <v>4</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="60" customHeight="1">
@@ -9405,17 +9405,17 @@
         <v>245</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="4"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="60" customHeight="1">
@@ -9426,17 +9426,17 @@
         <v>247</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="60" customHeight="1">
@@ -9447,17 +9447,17 @@
         <v>249</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="4"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="60" customHeight="1">
@@ -9468,23 +9468,23 @@
         <v>251</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="3">
         <v>3</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="60" customHeight="1">
@@ -9495,23 +9495,23 @@
         <v>253</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="3">
         <v>4</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="60" customHeight="1">
@@ -9522,17 +9522,17 @@
         <v>255</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="60" customHeight="1">
@@ -9543,23 +9543,23 @@
         <v>257</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="3">
         <v>4</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="60" customHeight="1">
@@ -9570,23 +9570,23 @@
         <v>259</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="3">
         <v>3</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="60" customHeight="1">
@@ -9597,17 +9597,17 @@
         <v>261</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="4"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="60" customHeight="1">
@@ -9618,17 +9618,17 @@
         <v>263</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="4"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
   </sheetData>
@@ -9710,7 +9710,7 @@
         <v>270</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E2" s="3">
         <v>-0.6</v>
@@ -9719,13 +9719,13 @@
         <v>271</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1">
@@ -9739,22 +9739,22 @@
         <v>270</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1">
@@ -9768,7 +9768,7 @@
         <v>270</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="s">
@@ -9776,10 +9776,10 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1">
@@ -9793,7 +9793,7 @@
         <v>270</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
@@ -9801,10 +9801,10 @@
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1">
@@ -9818,7 +9818,7 @@
         <v>276</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E6" s="3">
         <v>0.8</v>
@@ -9827,13 +9827,13 @@
         <v>271</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1">
@@ -9847,22 +9847,22 @@
         <v>276</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>1318</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>1347</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>1319</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1">
@@ -9876,7 +9876,7 @@
         <v>276</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E8" s="3">
         <v>0.6</v>
@@ -9885,13 +9885,13 @@
         <v>271</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1">
@@ -9905,7 +9905,7 @@
         <v>276</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
@@ -9913,10 +9913,10 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="60" customHeight="1">
@@ -9930,7 +9930,7 @@
         <v>278</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
@@ -9938,10 +9938,10 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="60" customHeight="1">
@@ -9955,7 +9955,7 @@
         <v>278</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>271</v>
@@ -9963,10 +9963,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="60" customHeight="1">
@@ -9980,7 +9980,7 @@
         <v>278</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
@@ -9988,10 +9988,10 @@
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1">
@@ -10005,7 +10005,7 @@
         <v>278</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
@@ -10013,10 +10013,10 @@
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60" customHeight="1">
@@ -10030,7 +10030,7 @@
         <v>280</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E14" s="3">
         <v>-0.7</v>
@@ -10039,13 +10039,13 @@
         <v>271</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="60" customHeight="1">
@@ -10059,22 +10059,22 @@
         <v>280</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="60" customHeight="1">
@@ -10088,7 +10088,7 @@
         <v>280</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E16" s="3">
         <v>0.6</v>
@@ -10097,13 +10097,13 @@
         <v>271</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" customHeight="1">
@@ -10117,7 +10117,7 @@
         <v>280</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="s">
@@ -10125,10 +10125,10 @@
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" customHeight="1">
@@ -10142,7 +10142,7 @@
         <v>282</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -10151,13 +10151,13 @@
         <v>271</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" customHeight="1">
@@ -10171,22 +10171,22 @@
         <v>282</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" customHeight="1">
@@ -10200,7 +10200,7 @@
         <v>282</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
@@ -10208,10 +10208,10 @@
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" customHeight="1">
@@ -10225,7 +10225,7 @@
         <v>282</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
@@ -10233,10 +10233,10 @@
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" customHeight="1">
@@ -10250,7 +10250,7 @@
         <v>284</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         <v>271</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" customHeight="1">
@@ -10279,22 +10279,22 @@
         <v>284</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" customHeight="1">
@@ -10308,7 +10308,7 @@
         <v>284</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="s">
@@ -10316,10 +10316,10 @@
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" customHeight="1">
@@ -10333,7 +10333,7 @@
         <v>284</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="5" t="s">
@@ -10341,10 +10341,10 @@
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" customHeight="1">
@@ -10358,7 +10358,7 @@
         <v>286</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
@@ -10366,10 +10366,10 @@
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" customHeight="1">
@@ -10383,7 +10383,7 @@
         <v>286</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>271</v>
@@ -10391,10 +10391,10 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" customHeight="1">
@@ -10408,7 +10408,7 @@
         <v>286</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E28" s="3">
         <v>0.6</v>
@@ -10417,13 +10417,13 @@
         <v>271</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" customHeight="1">
@@ -10437,7 +10437,7 @@
         <v>286</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E29" s="3">
         <v>0.6</v>
@@ -10446,13 +10446,13 @@
         <v>271</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" customHeight="1">
@@ -10466,7 +10466,7 @@
         <v>288</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="5" t="s">
@@ -10474,10 +10474,10 @@
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" customHeight="1">
@@ -10491,7 +10491,7 @@
         <v>288</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>271</v>
@@ -10499,10 +10499,10 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" customHeight="1">
@@ -10516,7 +10516,7 @@
         <v>288</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="5" t="s">
@@ -10524,10 +10524,10 @@
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="60" customHeight="1">
@@ -10541,7 +10541,7 @@
         <v>288</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="5" t="s">
@@ -10549,10 +10549,10 @@
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="60" customHeight="1">
@@ -10566,7 +10566,7 @@
         <v>290</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="5" t="s">
@@ -10574,10 +10574,10 @@
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="60" customHeight="1">
@@ -10591,7 +10591,7 @@
         <v>290</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>271</v>
@@ -10599,10 +10599,10 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="60" customHeight="1">
@@ -10616,7 +10616,7 @@
         <v>290</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="5" t="s">
@@ -10624,10 +10624,10 @@
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="60" customHeight="1">
@@ -10641,7 +10641,7 @@
         <v>290</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="5" t="s">
@@ -10649,10 +10649,10 @@
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="60" customHeight="1">
@@ -10666,7 +10666,7 @@
         <v>292</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="5" t="s">
@@ -10674,10 +10674,10 @@
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="60" customHeight="1">
@@ -10691,7 +10691,7 @@
         <v>292</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>271</v>
@@ -10699,10 +10699,10 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="60" customHeight="1">
@@ -10716,7 +10716,7 @@
         <v>292</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="5" t="s">
@@ -10724,10 +10724,10 @@
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="60" customHeight="1">
@@ -10741,7 +10741,7 @@
         <v>292</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="5" t="s">
@@ -10749,10 +10749,10 @@
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="60" customHeight="1">
@@ -10766,7 +10766,7 @@
         <v>294</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="5" t="s">
@@ -10774,10 +10774,10 @@
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="60" customHeight="1">
@@ -10791,7 +10791,7 @@
         <v>294</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>271</v>
@@ -10799,10 +10799,10 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="60" customHeight="1">
@@ -10816,7 +10816,7 @@
         <v>294</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="5" t="s">
@@ -10824,10 +10824,10 @@
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="60" customHeight="1">
@@ -10841,7 +10841,7 @@
         <v>294</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="5" t="s">
@@ -10849,10 +10849,10 @@
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="60" customHeight="1">
@@ -10866,7 +10866,7 @@
         <v>296</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="5" t="s">
@@ -10874,10 +10874,10 @@
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="60" customHeight="1">
@@ -10891,7 +10891,7 @@
         <v>296</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>271</v>
@@ -10899,10 +10899,10 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="60" customHeight="1">
@@ -10916,7 +10916,7 @@
         <v>296</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="5" t="s">
@@ -10924,10 +10924,10 @@
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="60" customHeight="1">
@@ -10941,7 +10941,7 @@
         <v>296</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="5" t="s">
@@ -10949,10 +10949,10 @@
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="60" customHeight="1">
@@ -10966,7 +10966,7 @@
         <v>298</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="5" t="s">
@@ -10974,10 +10974,10 @@
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="60" customHeight="1">
@@ -10991,7 +10991,7 @@
         <v>298</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>271</v>
@@ -10999,10 +10999,10 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="60" customHeight="1">
@@ -11016,7 +11016,7 @@
         <v>298</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="5" t="s">
@@ -11024,10 +11024,10 @@
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="60" customHeight="1">
@@ -11041,7 +11041,7 @@
         <v>298</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="5" t="s">
@@ -11049,10 +11049,10 @@
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="60" customHeight="1">
@@ -11066,7 +11066,7 @@
         <v>300</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="5" t="s">
@@ -11074,10 +11074,10 @@
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="60" customHeight="1">
@@ -11091,7 +11091,7 @@
         <v>300</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>271</v>
@@ -11099,10 +11099,10 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="60" customHeight="1">
@@ -11116,7 +11116,7 @@
         <v>300</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="5" t="s">
@@ -11124,10 +11124,10 @@
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="60" customHeight="1">
@@ -11141,7 +11141,7 @@
         <v>300</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="5" t="s">
@@ -11149,10 +11149,10 @@
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="60" customHeight="1">
@@ -11166,7 +11166,7 @@
         <v>302</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="5" t="s">
@@ -11174,10 +11174,10 @@
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="60" customHeight="1">
@@ -11191,7 +11191,7 @@
         <v>302</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>271</v>
@@ -11199,10 +11199,10 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="60" customHeight="1">
@@ -11216,7 +11216,7 @@
         <v>302</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="5" t="s">
@@ -11224,10 +11224,10 @@
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="60" customHeight="1">
@@ -11241,7 +11241,7 @@
         <v>302</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="5" t="s">
@@ -11249,10 +11249,10 @@
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="60" customHeight="1">
@@ -11266,7 +11266,7 @@
         <v>304</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="5" t="s">
@@ -11274,10 +11274,10 @@
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="60" customHeight="1">
@@ -11291,7 +11291,7 @@
         <v>304</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>271</v>
@@ -11299,10 +11299,10 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="60" customHeight="1">
@@ -11316,7 +11316,7 @@
         <v>304</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="5" t="s">
@@ -11324,10 +11324,10 @@
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="60" customHeight="1">
@@ -11341,7 +11341,7 @@
         <v>304</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="5" t="s">
@@ -11349,10 +11349,10 @@
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="60" customHeight="1">
@@ -11366,7 +11366,7 @@
         <v>306</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="5" t="s">
@@ -11374,10 +11374,10 @@
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="60" customHeight="1">
@@ -11391,7 +11391,7 @@
         <v>306</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>271</v>
@@ -11399,10 +11399,10 @@
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="60" customHeight="1">
@@ -11416,7 +11416,7 @@
         <v>306</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="5" t="s">
@@ -11424,10 +11424,10 @@
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="60" customHeight="1">
@@ -11441,7 +11441,7 @@
         <v>306</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="5" t="s">
@@ -11449,10 +11449,10 @@
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="60" customHeight="1">
@@ -11466,7 +11466,7 @@
         <v>308</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="5" t="s">
@@ -11474,10 +11474,10 @@
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="60" customHeight="1">
@@ -11491,7 +11491,7 @@
         <v>308</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>271</v>
@@ -11499,10 +11499,10 @@
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="60" customHeight="1">
@@ -11516,7 +11516,7 @@
         <v>308</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E72" s="3">
         <v>0.6</v>
@@ -11525,13 +11525,13 @@
         <v>271</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="60" customHeight="1">
@@ -11545,7 +11545,7 @@
         <v>308</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="5" t="s">
@@ -11553,10 +11553,10 @@
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="60" customHeight="1">
@@ -11570,7 +11570,7 @@
         <v>310</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="5" t="s">
@@ -11578,10 +11578,10 @@
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="60" customHeight="1">
@@ -11595,7 +11595,7 @@
         <v>310</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>271</v>
@@ -11603,10 +11603,10 @@
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="60" customHeight="1">
@@ -11620,7 +11620,7 @@
         <v>310</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="5" t="s">
@@ -11628,10 +11628,10 @@
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="60" customHeight="1">
@@ -11645,7 +11645,7 @@
         <v>310</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="5" t="s">
@@ -11653,10 +11653,10 @@
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="60" customHeight="1">
@@ -11670,7 +11670,7 @@
         <v>312</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="5" t="s">
@@ -11678,10 +11678,10 @@
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="60" customHeight="1">
@@ -11695,7 +11695,7 @@
         <v>312</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>271</v>
@@ -11703,10 +11703,10 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="60" customHeight="1">
@@ -11720,7 +11720,7 @@
         <v>312</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="5" t="s">
@@ -11728,10 +11728,10 @@
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="60" customHeight="1">
@@ -11745,7 +11745,7 @@
         <v>312</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="5" t="s">
@@ -11753,10 +11753,10 @@
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="60" customHeight="1">
@@ -11770,7 +11770,7 @@
         <v>314</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="5" t="s">
@@ -11778,10 +11778,10 @@
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="60" customHeight="1">
@@ -11795,7 +11795,7 @@
         <v>314</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>271</v>
@@ -11803,10 +11803,10 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="60" customHeight="1">
@@ -11820,7 +11820,7 @@
         <v>314</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E84" s="3">
         <v>0.6</v>
@@ -11829,13 +11829,13 @@
         <v>271</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="60" customHeight="1">
@@ -11849,7 +11849,7 @@
         <v>314</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E85" s="3">
         <v>0.6</v>
@@ -11858,13 +11858,13 @@
         <v>271</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="60" customHeight="1">
@@ -11878,7 +11878,7 @@
         <v>316</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="5" t="s">
@@ -11886,10 +11886,10 @@
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="60" customHeight="1">
@@ -11903,7 +11903,7 @@
         <v>316</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>271</v>
@@ -11911,10 +11911,10 @@
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="60" customHeight="1">
@@ -11928,7 +11928,7 @@
         <v>316</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="5" t="s">
@@ -11936,10 +11936,10 @@
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="60" customHeight="1">
@@ -11953,7 +11953,7 @@
         <v>316</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="5" t="s">
@@ -11961,10 +11961,10 @@
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="60" customHeight="1">
@@ -11978,7 +11978,7 @@
         <v>318</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="5" t="s">
@@ -11986,10 +11986,10 @@
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="60" customHeight="1">
@@ -12003,7 +12003,7 @@
         <v>318</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>271</v>
@@ -12011,10 +12011,10 @@
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="60" customHeight="1">
@@ -12028,7 +12028,7 @@
         <v>318</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E92" s="3">
         <v>0.6</v>
@@ -12037,13 +12037,13 @@
         <v>271</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="60" customHeight="1">
@@ -12057,7 +12057,7 @@
         <v>318</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="5" t="s">
@@ -12065,10 +12065,10 @@
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="60" customHeight="1">
@@ -12082,7 +12082,7 @@
         <v>320</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E94" s="3">
         <v>-0.7</v>
@@ -12091,13 +12091,13 @@
         <v>271</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="60" customHeight="1">
@@ -12111,22 +12111,22 @@
         <v>320</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="60" customHeight="1">
@@ -12140,7 +12140,7 @@
         <v>320</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E96" s="3">
         <v>0.6</v>
@@ -12149,13 +12149,13 @@
         <v>271</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="60" customHeight="1">
@@ -12169,7 +12169,7 @@
         <v>320</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E97" s="3">
         <v>0</v>
@@ -12178,13 +12178,13 @@
         <v>271</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="60" customHeight="1">
@@ -12198,7 +12198,7 @@
         <v>322</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="5" t="s">
@@ -12206,10 +12206,10 @@
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="60" customHeight="1">
@@ -12223,7 +12223,7 @@
         <v>322</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>271</v>
@@ -12231,10 +12231,10 @@
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="60" customHeight="1">
@@ -12248,7 +12248,7 @@
         <v>322</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E100" s="3">
         <v>0.6</v>
@@ -12257,13 +12257,13 @@
         <v>271</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="60" customHeight="1">
@@ -12277,7 +12277,7 @@
         <v>322</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="5" t="s">
@@ -12285,10 +12285,10 @@
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="60" customHeight="1">
@@ -12302,7 +12302,7 @@
         <v>324</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="5" t="s">
@@ -12310,10 +12310,10 @@
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="60" customHeight="1">
@@ -12327,7 +12327,7 @@
         <v>324</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>271</v>
@@ -12335,10 +12335,10 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="60" customHeight="1">
@@ -12352,7 +12352,7 @@
         <v>324</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E104" s="3">
         <v>0.6</v>
@@ -12361,13 +12361,13 @@
         <v>271</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="60" customHeight="1">
@@ -12381,7 +12381,7 @@
         <v>324</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E105" s="3">
         <v>0.6</v>
@@ -12390,13 +12390,13 @@
         <v>271</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="60" customHeight="1">
@@ -12410,7 +12410,7 @@
         <v>326</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="5" t="s">
@@ -12418,10 +12418,10 @@
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="60" customHeight="1">
@@ -12435,7 +12435,7 @@
         <v>326</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>271</v>
@@ -12443,10 +12443,10 @@
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="60" customHeight="1">
@@ -12460,7 +12460,7 @@
         <v>326</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="5" t="s">
@@ -12468,10 +12468,10 @@
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="60" customHeight="1">
@@ -12485,7 +12485,7 @@
         <v>326</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="5" t="s">
@@ -12493,10 +12493,10 @@
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="60" customHeight="1">
@@ -12510,7 +12510,7 @@
         <v>328</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="5" t="s">
@@ -12518,10 +12518,10 @@
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="60" customHeight="1">
@@ -12535,7 +12535,7 @@
         <v>328</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>271</v>
@@ -12543,10 +12543,10 @@
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="60" customHeight="1">
@@ -12560,7 +12560,7 @@
         <v>328</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="5" t="s">
@@ -12568,10 +12568,10 @@
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="60" customHeight="1">
@@ -12585,7 +12585,7 @@
         <v>328</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="5" t="s">
@@ -12593,10 +12593,10 @@
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="60" customHeight="1">
@@ -12610,7 +12610,7 @@
         <v>330</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E114" s="3">
         <v>-0.7</v>
@@ -12619,13 +12619,13 @@
         <v>271</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="60" customHeight="1">
@@ -12639,22 +12639,22 @@
         <v>330</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="60" customHeight="1">
@@ -12668,7 +12668,7 @@
         <v>330</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="5" t="s">
@@ -12676,10 +12676,10 @@
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="60" customHeight="1">
@@ -12693,7 +12693,7 @@
         <v>330</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="5" t="s">
@@ -12701,10 +12701,10 @@
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="60" customHeight="1">
@@ -12718,7 +12718,7 @@
         <v>332</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E118" s="3">
         <v>-0.7</v>
@@ -12727,13 +12727,13 @@
         <v>271</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="60" customHeight="1">
@@ -12747,22 +12747,22 @@
         <v>332</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="60" customHeight="1">
@@ -12776,7 +12776,7 @@
         <v>332</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="5" t="s">
@@ -12784,10 +12784,10 @@
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="60" customHeight="1">
@@ -12801,7 +12801,7 @@
         <v>332</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="5" t="s">
@@ -12809,10 +12809,10 @@
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="60" customHeight="1">
@@ -12826,7 +12826,7 @@
         <v>334</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="5" t="s">
@@ -12834,10 +12834,10 @@
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="60" customHeight="1">
@@ -12851,7 +12851,7 @@
         <v>334</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>271</v>
@@ -12859,10 +12859,10 @@
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
       <c r="H123" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="60" customHeight="1">
@@ -12876,7 +12876,7 @@
         <v>334</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E124" s="3">
         <v>0</v>
@@ -12885,13 +12885,13 @@
         <v>271</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="60" customHeight="1">
@@ -12905,7 +12905,7 @@
         <v>334</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="5" t="s">
@@ -12913,10 +12913,10 @@
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="60" customHeight="1">
@@ -12930,7 +12930,7 @@
         <v>336</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="5" t="s">
@@ -12938,10 +12938,10 @@
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="60" customHeight="1">
@@ -12955,7 +12955,7 @@
         <v>336</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>271</v>
@@ -12963,10 +12963,10 @@
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
       <c r="H127" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="60" customHeight="1">
@@ -12980,7 +12980,7 @@
         <v>336</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="5" t="s">
@@ -12988,10 +12988,10 @@
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="60" customHeight="1">
@@ -13005,7 +13005,7 @@
         <v>336</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="5" t="s">
@@ -13013,10 +13013,10 @@
       </c>
       <c r="G129" s="3"/>
       <c r="H129" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="60" customHeight="1">
@@ -13030,7 +13030,7 @@
         <v>338</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E130" s="3">
         <v>0</v>
@@ -13039,13 +13039,13 @@
         <v>271</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="60" customHeight="1">
@@ -13059,22 +13059,22 @@
         <v>338</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="60" customHeight="1">
@@ -13088,7 +13088,7 @@
         <v>338</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="5" t="s">
@@ -13096,10 +13096,10 @@
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="60" customHeight="1">
@@ -13113,7 +13113,7 @@
         <v>338</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="5" t="s">
@@ -13121,10 +13121,10 @@
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="60" customHeight="1">
@@ -13138,7 +13138,7 @@
         <v>340</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="5" t="s">
@@ -13146,10 +13146,10 @@
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="60" customHeight="1">
@@ -13163,7 +13163,7 @@
         <v>340</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>271</v>
@@ -13171,10 +13171,10 @@
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
       <c r="H135" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="60" customHeight="1">
@@ -13188,7 +13188,7 @@
         <v>340</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E136" s="3">
         <v>0.6</v>
@@ -13197,13 +13197,13 @@
         <v>271</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="60" customHeight="1">
@@ -13217,7 +13217,7 @@
         <v>340</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="5" t="s">
@@ -13225,10 +13225,10 @@
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="60" customHeight="1">
@@ -13242,7 +13242,7 @@
         <v>342</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="5" t="s">
@@ -13250,10 +13250,10 @@
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="60" customHeight="1">
@@ -13267,7 +13267,7 @@
         <v>342</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>271</v>
@@ -13275,10 +13275,10 @@
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
       <c r="H139" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="60" customHeight="1">
@@ -13292,7 +13292,7 @@
         <v>342</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="5" t="s">
@@ -13300,10 +13300,10 @@
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="60" customHeight="1">
@@ -13317,7 +13317,7 @@
         <v>342</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="5" t="s">
@@ -13325,10 +13325,10 @@
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="60" customHeight="1">
@@ -13342,7 +13342,7 @@
         <v>344</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="5" t="s">
@@ -13350,10 +13350,10 @@
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="60" customHeight="1">
@@ -13367,7 +13367,7 @@
         <v>344</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>271</v>
@@ -13375,10 +13375,10 @@
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
       <c r="H143" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="60" customHeight="1">
@@ -13392,7 +13392,7 @@
         <v>344</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="5" t="s">
@@ -13400,10 +13400,10 @@
       </c>
       <c r="G144" s="3"/>
       <c r="H144" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="60" customHeight="1">
@@ -13417,7 +13417,7 @@
         <v>344</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="5" t="s">
@@ -13425,10 +13425,10 @@
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
   </sheetData>
